--- a/docs/sap490/generated/Test_Scenario_IDTS_SAP01_en_v0.3.xlsx
+++ b/docs/sap490/generated/Test_Scenario_IDTS_SAP01_en_v0.3.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="184">
   <si>
     <t xml:space="preserve">Test Scenario</t>
   </si>
@@ -477,7 +477,11 @@
     <t xml:space="preserve">FUNCTIONAL_UI_API / POSITIVE_NEGATIVE / HIGH</t>
   </si>
   <si>
-    <t xml:space="preserve">NOT_RUN</t>
+    <t xml:space="preserve">IDTS-100 automated acceptance under DonHV
+2026-07-24T20:42:48+07:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">docs/pm/evidence/idts-100/shared-qa-ai/render-ai-smoke.json, docs/pm/evidence/idts-100/shared-qa-ai-browser/all-review-actions/shared-qa-ai-browser.json</t>
   </si>
   <si>
     <t xml:space="preserve">Classify and assign by active responsibility
@@ -497,7 +501,8 @@
     <t xml:space="preserve">FUNCTIONAL_UI_API / POSITIVE_BOUNDARY / HIGH</t>
   </si>
   <si>
-    <t xml:space="preserve">IDTS-56</t>
+    <t xml:space="preserve">docs/pm/evidence/idts-100/shared-qa-lifecycle/shared-qa-lifecycle.json, docs/pm/evidence/idts-100/shared-qa-ai-browser/assignment/idts72-ai-browser-smoke.json
+IDTS-56</t>
   </si>
   <si>
     <t xml:space="preserve">Create without an assignee
@@ -517,6 +522,9 @@
     <t xml:space="preserve">FUNCTIONAL_UI_API / BOUNDARY / HIGH</t>
   </si>
   <si>
+    <t xml:space="preserve">docs/pm/evidence/idts-100/shared-qa-lifecycle/shared-qa-lifecycle.json</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reassign with history
 Objective: Verify authorized reassignment replaces one technical owner and records history.
 Req: SRS-FR-ASSIGN-004, SRS-FR-AUDIT-001
@@ -551,6 +559,9 @@
     <t xml:space="preserve">FUNCTIONAL_UI_API / POSITIVE_NEGATIVE_AUTHORIZATION / HIGH</t>
   </si>
   <si>
+    <t xml:space="preserve">docs/pm/evidence/idts-100/shared-qa-lifecycle/shared-qa-lifecycle.json, docs/pm/evidence/idts-100/shared-qa-email-brevo-20260724.md</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reject, correct and reassign
 Objective: Verify rejection is non-terminal and requires reason plus follow-up ownership.
 Req: SRS-FR-STATUS-003, SRS-FR-STATUS-004, SRS-FR-STATUS-009
@@ -621,7 +632,7 @@
     <t xml:space="preserve">FUNCTIONAL_HTTP_UI / POSITIVE_NEGATIVE_PERSISTENCE / HIGH</t>
   </si>
   <si>
-    <t xml:space="preserve">scripts/qa/test-comments-attachments.ps1
+    <t xml:space="preserve">docs/pm/evidence/idts-100/shared-qa-attachments/idts73-create-attachments-browser.json, docs/pm/evidence/idts-100/shared-qa-attachments/delete-verification-20260724.md
 IDTS-55</t>
   </si>
   <si>
@@ -690,7 +701,8 @@
     <t xml:space="preserve">FUNCTIONAL_UI_API / POSITIVE_NEGATIVE_FAILURE_RECOVERY / HIGH</t>
   </si>
   <si>
-    <t xml:space="preserve">IDTS-78</t>
+    <t xml:space="preserve">docs/pm/evidence/idts-100/shared-qa-ai/render-ai-smoke.json, docs/pm/evidence/idts-100/shared-qa-ai-browser/all-review-actions/shared-qa-ai-browser.json, docs/pm/evidence/idts-100/shared-qa-ai-browser/assignment/idts72-ai-browser-smoke.json
+IDTS-78</t>
   </si>
 </sst>
 </file>
@@ -7932,17 +7944,21 @@
       <c r="BR17" s="75"/>
       <c r="BS17" s="75"/>
       <c r="BT17" s="75"/>
-      <c r="BU17" s="76"/>
+      <c r="BU17" s="76" t="s">
+        <v>129</v>
+      </c>
       <c r="BV17" s="76"/>
       <c r="BW17" s="76"/>
       <c r="BX17" s="76"/>
       <c r="BY17" s="76"/>
       <c r="BZ17" s="76"/>
       <c r="CA17" s="69" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="CB17" s="69"/>
-      <c r="CC17" s="77"/>
+      <c r="CC17" s="77" t="s">
+        <v>130</v>
+      </c>
       <c r="CD17" s="77"/>
       <c r="CE17" s="77"/>
       <c r="CF17" s="77"/>
@@ -7958,7 +7974,7 @@
       <c r="C18" s="79"/>
       <c r="D18" s="79"/>
       <c r="E18" s="74" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F18" s="74"/>
       <c r="G18" s="74"/>
@@ -7980,7 +7996,7 @@
       <c r="W18" s="74"/>
       <c r="X18" s="74"/>
       <c r="Y18" s="73" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Z18" s="73"/>
       <c r="AA18" s="73"/>
@@ -7999,7 +8015,7 @@
       <c r="AN18" s="73"/>
       <c r="AO18" s="73"/>
       <c r="AP18" s="74" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AQ18" s="74"/>
       <c r="AR18" s="74"/>
@@ -8026,25 +8042,27 @@
       <c r="BM18" s="74"/>
       <c r="BN18" s="74"/>
       <c r="BO18" s="75" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="BP18" s="75"/>
       <c r="BQ18" s="75"/>
       <c r="BR18" s="75"/>
       <c r="BS18" s="75"/>
       <c r="BT18" s="75"/>
-      <c r="BU18" s="76"/>
+      <c r="BU18" s="76" t="s">
+        <v>129</v>
+      </c>
       <c r="BV18" s="76"/>
       <c r="BW18" s="76"/>
       <c r="BX18" s="76"/>
       <c r="BY18" s="76"/>
       <c r="BZ18" s="76"/>
       <c r="CA18" s="69" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="CB18" s="69"/>
       <c r="CC18" s="77" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="CD18" s="77"/>
       <c r="CE18" s="77"/>
@@ -8061,7 +8079,7 @@
       <c r="C19" s="71"/>
       <c r="D19" s="71"/>
       <c r="E19" s="72" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F19" s="72"/>
       <c r="G19" s="72"/>
@@ -8083,7 +8101,7 @@
       <c r="W19" s="72"/>
       <c r="X19" s="72"/>
       <c r="Y19" s="73" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Z19" s="73"/>
       <c r="AA19" s="73"/>
@@ -8102,7 +8120,7 @@
       <c r="AN19" s="73"/>
       <c r="AO19" s="73"/>
       <c r="AP19" s="74" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AQ19" s="74"/>
       <c r="AR19" s="74"/>
@@ -8129,24 +8147,28 @@
       <c r="BM19" s="74"/>
       <c r="BN19" s="74"/>
       <c r="BO19" s="75" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BP19" s="75"/>
       <c r="BQ19" s="75"/>
       <c r="BR19" s="75"/>
       <c r="BS19" s="75"/>
       <c r="BT19" s="75"/>
-      <c r="BU19" s="76"/>
+      <c r="BU19" s="76" t="s">
+        <v>129</v>
+      </c>
       <c r="BV19" s="76"/>
       <c r="BW19" s="76"/>
       <c r="BX19" s="76"/>
       <c r="BY19" s="76"/>
       <c r="BZ19" s="76"/>
       <c r="CA19" s="69" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="CB19" s="69"/>
-      <c r="CC19" s="77"/>
+      <c r="CC19" s="77" t="s">
+        <v>140</v>
+      </c>
       <c r="CD19" s="77"/>
       <c r="CE19" s="77"/>
       <c r="CF19" s="77"/>
@@ -8162,7 +8184,7 @@
       <c r="C20" s="79"/>
       <c r="D20" s="79"/>
       <c r="E20" s="74" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F20" s="74"/>
       <c r="G20" s="74"/>
@@ -8184,7 +8206,7 @@
       <c r="W20" s="74"/>
       <c r="X20" s="74"/>
       <c r="Y20" s="73" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Z20" s="73"/>
       <c r="AA20" s="73"/>
@@ -8203,7 +8225,7 @@
       <c r="AN20" s="73"/>
       <c r="AO20" s="73"/>
       <c r="AP20" s="74" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AQ20" s="74"/>
       <c r="AR20" s="74"/>
@@ -8230,24 +8252,28 @@
       <c r="BM20" s="74"/>
       <c r="BN20" s="74"/>
       <c r="BO20" s="75" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="BP20" s="75"/>
       <c r="BQ20" s="75"/>
       <c r="BR20" s="75"/>
       <c r="BS20" s="75"/>
       <c r="BT20" s="75"/>
-      <c r="BU20" s="76"/>
+      <c r="BU20" s="76" t="s">
+        <v>129</v>
+      </c>
       <c r="BV20" s="76"/>
       <c r="BW20" s="76"/>
       <c r="BX20" s="76"/>
       <c r="BY20" s="76"/>
       <c r="BZ20" s="76"/>
       <c r="CA20" s="69" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="CB20" s="69"/>
-      <c r="CC20" s="77"/>
+      <c r="CC20" s="77" t="s">
+        <v>140</v>
+      </c>
       <c r="CD20" s="77"/>
       <c r="CE20" s="77"/>
       <c r="CF20" s="77"/>
@@ -8263,7 +8289,7 @@
       <c r="C21" s="79"/>
       <c r="D21" s="79"/>
       <c r="E21" s="74" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F21" s="74"/>
       <c r="G21" s="74"/>
@@ -8285,7 +8311,7 @@
       <c r="W21" s="74"/>
       <c r="X21" s="74"/>
       <c r="Y21" s="73" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Z21" s="73"/>
       <c r="AA21" s="73"/>
@@ -8304,7 +8330,7 @@
       <c r="AN21" s="73"/>
       <c r="AO21" s="73"/>
       <c r="AP21" s="74" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AQ21" s="74"/>
       <c r="AR21" s="74"/>
@@ -8331,24 +8357,28 @@
       <c r="BM21" s="74"/>
       <c r="BN21" s="74"/>
       <c r="BO21" s="75" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BP21" s="75"/>
       <c r="BQ21" s="75"/>
       <c r="BR21" s="75"/>
       <c r="BS21" s="75"/>
       <c r="BT21" s="75"/>
-      <c r="BU21" s="76"/>
+      <c r="BU21" s="76" t="s">
+        <v>129</v>
+      </c>
       <c r="BV21" s="76"/>
       <c r="BW21" s="76"/>
       <c r="BX21" s="76"/>
       <c r="BY21" s="76"/>
       <c r="BZ21" s="76"/>
       <c r="CA21" s="69" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="CB21" s="69"/>
-      <c r="CC21" s="77"/>
+      <c r="CC21" s="77" t="s">
+        <v>149</v>
+      </c>
       <c r="CD21" s="77"/>
       <c r="CE21" s="77"/>
       <c r="CF21" s="77"/>
@@ -8364,7 +8394,7 @@
       <c r="C22" s="79"/>
       <c r="D22" s="79"/>
       <c r="E22" s="74" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F22" s="74"/>
       <c r="G22" s="74"/>
@@ -8386,7 +8416,7 @@
       <c r="W22" s="74"/>
       <c r="X22" s="74"/>
       <c r="Y22" s="73" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Z22" s="73"/>
       <c r="AA22" s="73"/>
@@ -8405,7 +8435,7 @@
       <c r="AN22" s="73"/>
       <c r="AO22" s="73"/>
       <c r="AP22" s="74" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AQ22" s="74"/>
       <c r="AR22" s="74"/>
@@ -8439,17 +8469,21 @@
       <c r="BR22" s="75"/>
       <c r="BS22" s="75"/>
       <c r="BT22" s="75"/>
-      <c r="BU22" s="76"/>
+      <c r="BU22" s="76" t="s">
+        <v>129</v>
+      </c>
       <c r="BV22" s="76"/>
       <c r="BW22" s="76"/>
       <c r="BX22" s="76"/>
       <c r="BY22" s="76"/>
       <c r="BZ22" s="76"/>
       <c r="CA22" s="69" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="CB22" s="69"/>
-      <c r="CC22" s="77"/>
+      <c r="CC22" s="77" t="s">
+        <v>149</v>
+      </c>
       <c r="CD22" s="77"/>
       <c r="CE22" s="77"/>
       <c r="CF22" s="77"/>
@@ -8465,7 +8499,7 @@
       <c r="C23" s="79"/>
       <c r="D23" s="79"/>
       <c r="E23" s="74" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F23" s="74"/>
       <c r="G23" s="74"/>
@@ -8487,7 +8521,7 @@
       <c r="W23" s="74"/>
       <c r="X23" s="74"/>
       <c r="Y23" s="73" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Z23" s="73"/>
       <c r="AA23" s="73"/>
@@ -8506,7 +8540,7 @@
       <c r="AN23" s="73"/>
       <c r="AO23" s="73"/>
       <c r="AP23" s="74" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AQ23" s="74"/>
       <c r="AR23" s="74"/>
@@ -8540,17 +8574,21 @@
       <c r="BR23" s="75"/>
       <c r="BS23" s="75"/>
       <c r="BT23" s="75"/>
-      <c r="BU23" s="76"/>
+      <c r="BU23" s="76" t="s">
+        <v>129</v>
+      </c>
       <c r="BV23" s="76"/>
       <c r="BW23" s="76"/>
       <c r="BX23" s="76"/>
       <c r="BY23" s="76"/>
       <c r="BZ23" s="76"/>
       <c r="CA23" s="69" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="CB23" s="69"/>
-      <c r="CC23" s="77"/>
+      <c r="CC23" s="77" t="s">
+        <v>149</v>
+      </c>
       <c r="CD23" s="77"/>
       <c r="CE23" s="77"/>
       <c r="CF23" s="77"/>
@@ -8566,7 +8604,7 @@
       <c r="C24" s="79"/>
       <c r="D24" s="79"/>
       <c r="E24" s="74" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F24" s="74"/>
       <c r="G24" s="74"/>
@@ -8588,7 +8626,7 @@
       <c r="W24" s="74"/>
       <c r="X24" s="74"/>
       <c r="Y24" s="73" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Z24" s="73"/>
       <c r="AA24" s="73"/>
@@ -8607,7 +8645,7 @@
       <c r="AN24" s="73"/>
       <c r="AO24" s="73"/>
       <c r="AP24" s="74" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AQ24" s="74"/>
       <c r="AR24" s="74"/>
@@ -8634,7 +8672,7 @@
       <c r="BM24" s="74"/>
       <c r="BN24" s="74"/>
       <c r="BO24" s="75" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="BP24" s="75"/>
       <c r="BQ24" s="75"/>
@@ -8642,7 +8680,7 @@
       <c r="BS24" s="75"/>
       <c r="BT24" s="75"/>
       <c r="BU24" s="76" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="BV24" s="76"/>
       <c r="BW24" s="76"/>
@@ -8654,7 +8692,7 @@
       </c>
       <c r="CB24" s="69"/>
       <c r="CC24" s="77" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="CD24" s="77"/>
       <c r="CE24" s="77"/>
@@ -8671,7 +8709,7 @@
       <c r="C25" s="71"/>
       <c r="D25" s="71"/>
       <c r="E25" s="72" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F25" s="72"/>
       <c r="G25" s="72"/>
@@ -8693,7 +8731,7 @@
       <c r="W25" s="72"/>
       <c r="X25" s="72"/>
       <c r="Y25" s="73" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Z25" s="73"/>
       <c r="AA25" s="73"/>
@@ -8712,7 +8750,7 @@
       <c r="AN25" s="73"/>
       <c r="AO25" s="73"/>
       <c r="AP25" s="74" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AQ25" s="74"/>
       <c r="AR25" s="74"/>
@@ -8739,25 +8777,27 @@
       <c r="BM25" s="74"/>
       <c r="BN25" s="74"/>
       <c r="BO25" s="75" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="BP25" s="75"/>
       <c r="BQ25" s="75"/>
       <c r="BR25" s="75"/>
       <c r="BS25" s="75"/>
       <c r="BT25" s="75"/>
-      <c r="BU25" s="76"/>
+      <c r="BU25" s="76" t="s">
+        <v>129</v>
+      </c>
       <c r="BV25" s="76"/>
       <c r="BW25" s="76"/>
       <c r="BX25" s="76"/>
       <c r="BY25" s="76"/>
       <c r="BZ25" s="76"/>
       <c r="CA25" s="69" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="CB25" s="69"/>
       <c r="CC25" s="77" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="CD25" s="77"/>
       <c r="CE25" s="77"/>
@@ -8774,7 +8814,7 @@
       <c r="C26" s="79"/>
       <c r="D26" s="79"/>
       <c r="E26" s="74" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F26" s="74"/>
       <c r="G26" s="74"/>
@@ -8796,7 +8836,7 @@
       <c r="W26" s="74"/>
       <c r="X26" s="74"/>
       <c r="Y26" s="73" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Z26" s="73"/>
       <c r="AA26" s="73"/>
@@ -8815,7 +8855,7 @@
       <c r="AN26" s="73"/>
       <c r="AO26" s="73"/>
       <c r="AP26" s="74" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AQ26" s="74"/>
       <c r="AR26" s="74"/>
@@ -8842,7 +8882,7 @@
       <c r="BM26" s="74"/>
       <c r="BN26" s="74"/>
       <c r="BO26" s="75" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="BP26" s="75"/>
       <c r="BQ26" s="75"/>
@@ -8850,7 +8890,7 @@
       <c r="BS26" s="75"/>
       <c r="BT26" s="75"/>
       <c r="BU26" s="76" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="BV26" s="76"/>
       <c r="BW26" s="76"/>
@@ -8862,7 +8902,7 @@
       </c>
       <c r="CB26" s="69"/>
       <c r="CC26" s="77" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="CD26" s="77"/>
       <c r="CE26" s="77"/>
@@ -8879,7 +8919,7 @@
       <c r="C27" s="79"/>
       <c r="D27" s="79"/>
       <c r="E27" s="74" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F27" s="74"/>
       <c r="G27" s="74"/>
@@ -8901,7 +8941,7 @@
       <c r="W27" s="74"/>
       <c r="X27" s="74"/>
       <c r="Y27" s="73" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Z27" s="73"/>
       <c r="AA27" s="73"/>
@@ -8920,7 +8960,7 @@
       <c r="AN27" s="73"/>
       <c r="AO27" s="73"/>
       <c r="AP27" s="74" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AQ27" s="74"/>
       <c r="AR27" s="74"/>
@@ -8947,7 +8987,7 @@
       <c r="BM27" s="74"/>
       <c r="BN27" s="74"/>
       <c r="BO27" s="75" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="BP27" s="75"/>
       <c r="BQ27" s="75"/>
@@ -8955,7 +8995,7 @@
       <c r="BS27" s="75"/>
       <c r="BT27" s="75"/>
       <c r="BU27" s="76" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="BV27" s="76"/>
       <c r="BW27" s="76"/>
@@ -8967,7 +9007,7 @@
       </c>
       <c r="CB27" s="69"/>
       <c r="CC27" s="77" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="CD27" s="77"/>
       <c r="CE27" s="77"/>
@@ -8984,7 +9024,7 @@
       <c r="C28" s="79"/>
       <c r="D28" s="79"/>
       <c r="E28" s="74" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F28" s="74"/>
       <c r="G28" s="74"/>
@@ -9006,7 +9046,7 @@
       <c r="W28" s="74"/>
       <c r="X28" s="74"/>
       <c r="Y28" s="73" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Z28" s="73"/>
       <c r="AA28" s="73"/>
@@ -9025,7 +9065,7 @@
       <c r="AN28" s="73"/>
       <c r="AO28" s="73"/>
       <c r="AP28" s="74" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AQ28" s="74"/>
       <c r="AR28" s="74"/>
@@ -9052,25 +9092,27 @@
       <c r="BM28" s="74"/>
       <c r="BN28" s="74"/>
       <c r="BO28" s="75" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="BP28" s="75"/>
       <c r="BQ28" s="75"/>
       <c r="BR28" s="75"/>
       <c r="BS28" s="75"/>
       <c r="BT28" s="75"/>
-      <c r="BU28" s="76"/>
+      <c r="BU28" s="76" t="s">
+        <v>129</v>
+      </c>
       <c r="BV28" s="76"/>
       <c r="BW28" s="76"/>
       <c r="BX28" s="76"/>
       <c r="BY28" s="76"/>
       <c r="BZ28" s="76"/>
       <c r="CA28" s="69" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="CB28" s="69"/>
       <c r="CC28" s="77" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="CD28" s="77"/>
       <c r="CE28" s="77"/>
